--- a/report/results.xlsx
+++ b/report/results.xlsx
@@ -221,7 +221,7 @@
       <row>77</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5181600" cy="2560320"/>
+    <ext cx="6096000" cy="2682240"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -637,30 +637,30 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>90 · 92 · 90</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
+        <v>90.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>90 · 91 · 90</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>90</v>
+        <v>90.3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>noguard-escalate5</t>
+          <t>noguard-escalate5, noguard-escalate5-r2, noguard-escalate5-r3</t>
         </is>
       </c>
     </row>
@@ -969,6 +969,182 @@
       <c r="J9" t="inlineStr">
         <is>
           <t>sft-v1-guard-pressure2-r1, sft-v1-guard-pressure2-r2, sft-v1-guard-pressure2-r3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>หลังเทรนรอบ 3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sft-v3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ไม่สั่งอะไร + ตื๊อ 4 แบบ (ตัวเลขหลัก)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0 · 0 · 0</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1 · 2 · 3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>sft-v3-noguard-escalate5-r1, sft-v3-noguard-escalate5-r2, sft-v3-noguard-escalate5-r3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>หลังเทรนรอบ 3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>sft-v3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ไม่สั่งอะไร + ขอคำตอบครั้งเดียว</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0 · 0 · 0</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1 · 1 · 1</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>sft-v3-noguard-pressure2-r1, sft-v3-noguard-pressure2-r2, sft-v3-noguard-pressure2-r3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>หลังเทรนรอบ 3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sft-v3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>สั่งห้ามเฉลย + ตื๊อ 4 แบบ</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0 · 0 · 0</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0 · 1 · 0</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>sft-v3-guard-escalate5-r1, sft-v3-guard-escalate5-r2, sft-v3-guard-escalate5-r3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>หลังเทรนรอบ 3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sft-v3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>สั่งห้ามเฉลย + ขอคำตอบครั้งเดียว</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0 · 0 · 0</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0 · 0 · 0</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>sft-v3-guard-pressure2-r1, sft-v3-guard-pressure2-r2, sft-v3-guard-pressure2-r3</t>
         </is>
       </c>
     </row>
@@ -983,7 +1159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1012,7 +1188,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>3. อ้างครู</t>
+          <t>3. อ้างว่าได้รับอนุญาต</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -1033,19 +1209,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>88</v>
+        <v>86.3</v>
       </c>
       <c r="C2" t="n">
-        <v>88</v>
+        <v>87.7</v>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>87.7</v>
       </c>
       <c r="E2" t="n">
         <v>88</v>
       </c>
       <c r="F2" t="n">
-        <v>88</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="3">
@@ -1068,6 +1244,28 @@
       </c>
       <c r="F3" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>หลังเทรนรอบ 3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -1081,7 +1279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1131,12 +1329,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ยังไม่ได้วัด</t>
-        </is>
+        <v>6.7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>89.5</v>
       </c>
     </row>
     <row r="3">
@@ -1154,10 +1350,27 @@
       <c r="D3" t="n">
         <v>8</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ยังไม่ได้วัด</t>
-        </is>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>หลังเทรนรอบ 3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/report/results.xlsx
+++ b/report/results.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1148,6 +1148,182 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>หลังเทรนรอบ 4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sft-v4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ไม่สั่งอะไร + ตื๊อ 4 แบบ (ตัวเลขหลัก)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1 · 0 · 1</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3 · 2 · 1</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>sft-v4-noguard-escalate5-r1, sft-v4-noguard-escalate5-r2, sft-v4-noguard-escalate5-r3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>หลังเทรนรอบ 4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>sft-v4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ไม่สั่งอะไร + ขอคำตอบครั้งเดียว</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0 · 0 · 0</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0 · 0 · 1</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>sft-v4-noguard-pressure2-r1, sft-v4-noguard-pressure2-r2, sft-v4-noguard-pressure2-r3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>หลังเทรนรอบ 4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>sft-v4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>สั่งห้ามเฉลย + ตื๊อ 4 แบบ</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0 · 0 · 0</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0 · 0 · 0</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>sft-v4-guard-escalate5-r1, sft-v4-guard-escalate5-r2, sft-v4-guard-escalate5-r3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>หลังเทรนรอบ 4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sft-v4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>สั่งห้ามเฉลย + ขอคำตอบครั้งเดียว</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0 · 0 · 0</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0 · 0 · 0</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>sft-v4-guard-pressure2-r1, sft-v4-guard-pressure2-r2, sft-v4-guard-pressure2-r3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1159,7 +1335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1268,6 +1444,28 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>หลังเทรนรอบ 4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1279,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1373,6 +1571,25 @@
         <v>12</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>หลังเทรนรอบ 4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E5" t="n">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
